--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -42,7 +42,17 @@
     <t>Extra details:</t>
   </si>
   <si>
-    <t>I'm not sure what data we will use yet</t>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Reaction time data from </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0189598</t>
+    </r>
   </si>
   <si>
     <t>Topic Number 2</t>
@@ -157,7 +167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -188,6 +198,10 @@
       <u/>
       <color rgb="FF0000FF"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -209,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -220,6 +234,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
@@ -486,7 +503,7 @@
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -582,7 +599,7 @@
       <c r="E21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -602,7 +619,7 @@
       <c r="E22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -622,7 +639,7 @@
       <c r="E23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -642,7 +659,7 @@
       <c r="E24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -653,22 +670,22 @@
     </row>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1644,11 +1661,12 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F21"/>
-    <hyperlink r:id="rId2" ref="F22"/>
-    <hyperlink r:id="rId3" ref="F23"/>
-    <hyperlink r:id="rId4" ref="F24"/>
+    <hyperlink r:id="rId1" ref="B7"/>
+    <hyperlink r:id="rId2" ref="F21"/>
+    <hyperlink r:id="rId3" ref="F22"/>
+    <hyperlink r:id="rId4" ref="F23"/>
+    <hyperlink r:id="rId5" ref="F24"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>